--- a/artfynd/A 24189-2025 artfynd.xlsx
+++ b/artfynd/A 24189-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126142102</v>
       </c>
       <c r="B2" t="n">
-        <v>100521</v>
+        <v>100523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126140900</v>
       </c>
       <c r="B3" t="n">
-        <v>105446</v>
+        <v>105448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24189-2025 artfynd.xlsx
+++ b/artfynd/A 24189-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126142102</v>
       </c>
       <c r="B2" t="n">
-        <v>100523</v>
+        <v>100525</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126140900</v>
       </c>
       <c r="B3" t="n">
-        <v>105448</v>
+        <v>105450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24189-2025 artfynd.xlsx
+++ b/artfynd/A 24189-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126142102</v>
       </c>
       <c r="B2" t="n">
-        <v>100525</v>
+        <v>100527</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126140900</v>
       </c>
       <c r="B3" t="n">
-        <v>105450</v>
+        <v>105454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24189-2025 artfynd.xlsx
+++ b/artfynd/A 24189-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126142102</v>
       </c>
       <c r="B2" t="n">
-        <v>100527</v>
+        <v>100531</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126140900</v>
       </c>
       <c r="B3" t="n">
-        <v>105454</v>
+        <v>105467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24189-2025 artfynd.xlsx
+++ b/artfynd/A 24189-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126142102</v>
       </c>
       <c r="B2" t="n">
-        <v>100531</v>
+        <v>100534</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126140900</v>
       </c>
       <c r="B3" t="n">
-        <v>105467</v>
+        <v>105470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24189-2025 artfynd.xlsx
+++ b/artfynd/A 24189-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126142102</v>
       </c>
       <c r="B2" t="n">
-        <v>100534</v>
+        <v>100543</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126140900</v>
       </c>
       <c r="B3" t="n">
-        <v>105470</v>
+        <v>105479</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
